--- a/data/marketplace/MarketplaceData.xlsx
+++ b/data/marketplace/MarketplaceData.xlsx
@@ -5,22 +5,23 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://molinahealthcare-my.sharepoint.com/personal/naresh_jangid_molinahealthcare_com/Documents/Automation/molina_automation/PlanMaterialAutomation/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://molinahealthcare-my.sharepoint.com/personal/naresh_jangid_molinahealthcare_com/Documents/Automation/molina_automation/PlanMaterialAutomation/data/marketplace/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="11_716F432029E0BD565661024808129E37A02C6762" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A09D926A-A454-4662-B1D2-92195CE9671A}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_5625D102A8BF400918838D571C15BBF580A02A0F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CB97DC1-37DD-4E2F-9A90-81F054823C70}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Marketplace" sheetId="1" r:id="rId1"/>
+    <sheet name="DrugPharmacy" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="96">
   <si>
     <t>Run</t>
   </si>
@@ -46,34 +47,37 @@
     <t>Notes</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>NV</t>
+  </si>
+  <si>
+    <t>en</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>TC001 MP Toggle 2026/2027 (Forms and Documents) NV-EN</t>
+  </si>
+  <si>
+    <t>English - 2026/2027 coverage-year toggle validation on Forms &amp; Documents page for Nevada</t>
+  </si>
+  <si>
+    <t>es</t>
+  </si>
+  <si>
+    <t>TC002 MP Toggle 2026/2027 (Forms and Documents) NV-ES</t>
+  </si>
+  <si>
+    <t>Spanish (es-us) - 2026/2027 coverage-year toggle validation on Forms &amp; Documents page for Nevada</t>
+  </si>
+  <si>
     <t>N</t>
   </si>
   <si>
-    <t>NV</t>
-  </si>
-  <si>
-    <t>en</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>TC001 MP Toggle 2026/2027 (Forms and Documents) NV-EN</t>
-  </si>
-  <si>
-    <t>English - 2026/2027 coverage-year toggle validation on Forms &amp; Documents page for Nevada</t>
-  </si>
-  <si>
-    <t>es</t>
-  </si>
-  <si>
-    <t>TC002 MP Toggle 2026/2027 (Forms and Documents) NV-ES</t>
-  </si>
-  <si>
-    <t>Spanish (es-us) - 2026/2027 coverage-year toggle validation on Forms &amp; Documents page for Nevada</t>
-  </si>
-  <si>
-    <t>Y</t>
+    <t>FL</t>
   </si>
   <si>
     <t>TC003 MP Toggle 2026/2027 (Forms and Documents) FL-EN</t>
@@ -88,6 +92,9 @@
     <t>Spanish (es-us) - 2026/2027 coverage-year toggle validation on Forms &amp; Documents page for Florida</t>
   </si>
   <si>
+    <t>CA</t>
+  </si>
+  <si>
     <t>TC005 MP Toggle 2026/2027 (Forms and Documents) CA-EN</t>
   </si>
   <si>
@@ -100,6 +107,9 @@
     <t>Spanish (es-us) - 2026/2027 coverage-year toggle validation on Forms &amp; Documents page for California</t>
   </si>
   <si>
+    <t>ID</t>
+  </si>
+  <si>
     <t>TC007 MP Toggle 2026/2027 (Forms and Documents) ID-EN</t>
   </si>
   <si>
@@ -112,6 +122,9 @@
     <t>Spanish (es-us) - 2026/2027 coverage-year toggle validation on Forms &amp; Documents page for Idaho</t>
   </si>
   <si>
+    <t>MI</t>
+  </si>
+  <si>
     <t>TC009 MP Toggle 2026/2027 (Forms and Documents) MI-EN</t>
   </si>
   <si>
@@ -124,6 +137,9 @@
     <t>Spanish (es-us) - 2026/2027 coverage-year toggle validation on Forms &amp; Documents page for Michigan</t>
   </si>
   <si>
+    <t>IL</t>
+  </si>
+  <si>
     <t>TC011 MP Toggle 2026/2027 (Forms and Documents) IL-EN</t>
   </si>
   <si>
@@ -136,6 +152,9 @@
     <t>Spanish (es-us) - 2026/2027 coverage-year toggle validation on Forms &amp; Documents page for Illinois</t>
   </si>
   <si>
+    <t>NM</t>
+  </si>
+  <si>
     <t>TC013 MP Toggle 2026/2027 (Forms and Documents) NM-EN</t>
   </si>
   <si>
@@ -148,6 +167,9 @@
     <t>Spanish (es-us) - 2026/2027 coverage-year toggle validation on Forms &amp; Documents page for New Mexico</t>
   </si>
   <si>
+    <t>WA</t>
+  </si>
+  <si>
     <t>TC015 MP Toggle 2026/2027 (Forms and Documents) WA-EN</t>
   </si>
   <si>
@@ -160,6 +182,9 @@
     <t>Spanish (es-us) - 2026/2027 coverage-year toggle validation on Forms &amp; Documents page for Washington</t>
   </si>
   <si>
+    <t>OH</t>
+  </si>
+  <si>
     <t>TC017 MP Toggle 2026/2027 (Forms and Documents) OH-EN</t>
   </si>
   <si>
@@ -172,6 +197,9 @@
     <t>Spanish (es-us) - 2026/2027 coverage-year toggle validation on Forms &amp; Documents page for Ohio</t>
   </si>
   <si>
+    <t>TX</t>
+  </si>
+  <si>
     <t>TC019 MP Toggle 2026/2027 (Forms and Documents) TX-EN</t>
   </si>
   <si>
@@ -184,31 +212,103 @@
     <t>Spanish (es-us) - 2026/2027 coverage-year toggle validation on Forms &amp; Documents page for Texas</t>
   </si>
   <si>
-    <t>FL</t>
-  </si>
-  <si>
-    <t>CA</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>MI</t>
-  </si>
-  <si>
-    <t>IL</t>
-  </si>
-  <si>
-    <t>NM</t>
-  </si>
-  <si>
-    <t>WA</t>
-  </si>
-  <si>
-    <t>OH</t>
-  </si>
-  <si>
-    <t>TX</t>
+    <t>LinkLabel</t>
+  </si>
+  <si>
+    <t>ExpectedInitialUrl</t>
+  </si>
+  <si>
+    <t>ExpectedFinalUrl</t>
+  </si>
+  <si>
+    <t>SpanishLinkLabel</t>
+  </si>
+  <si>
+    <t>SpanishExpectedInitialUrl</t>
+  </si>
+  <si>
+    <t>SpanishExpectedFinalUrl</t>
+  </si>
+  <si>
+    <t>TC001 NV MP Find a Pharmacy Link</t>
+  </si>
+  <si>
+    <t>nv</t>
+  </si>
+  <si>
+    <t>Find a pharmacy|Pharmacy Location|Pharmacy Locator</t>
+  </si>
+  <si>
+    <t>https://www.caremark.com/wps/portal/.cmd/el?id=mo1li3nv44_1&amp;cmxtarget=FRAMED_LOCAL_PHARMACY&amp;newLogin=yes&amp;returnURL=http://www.caremark.com/framedLogoff.html</t>
+  </si>
+  <si>
+    <t>https://www.caremark.com/pharmacy/benefits/fast/oe/pharmacy-locator/search?fastStyle=OE&amp;oeFillDate=AUTO(01%2F01%2F2026)&amp;BlocksTenant=molina</t>
+  </si>
+  <si>
+    <t>ubicación|Localizador de farmacia|Localizador|Buscar farmacia|Encuentre una farmacia|Farmacia</t>
+  </si>
+  <si>
+    <t>TC002 CA MP Find a Pharmacy Link</t>
+  </si>
+  <si>
+    <t>ca</t>
+  </si>
+  <si>
+    <t>https://www.caremark.com/wps/portal/.cmd/el?id=mo1mp6ca_73&amp;cmxtarget=FRAMED_LOCAL_PHARMACY&amp;newLogin=yes&amp;returnURL=http://www.caremark.com/framedLogoff.html</t>
+  </si>
+  <si>
+    <t>TC003 ID MP Find a Pharmacy Link</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>https://www.caremark.com/wps/portal/.cmd/el?id=m0ly145km_19&amp;cmxtarget=FRAMED_LOCAL_PHARMACY&amp;newLogin=yes&amp;returnURL=http://www.caremark.com/framedLogoff.html</t>
+  </si>
+  <si>
+    <t>TC004 MI MP Find a Pharmacy Link</t>
+  </si>
+  <si>
+    <t>mi</t>
+  </si>
+  <si>
+    <t>https://www.caremark.com/wps/portal/.cmd/el?id=mo1mp6mi_86&amp;cmxtarget=FRAMED_LOCAL_PHARMACY&amp;newLogin=yes&amp;returnURL=http://www.caremark.com/framedLogoff.html</t>
+  </si>
+  <si>
+    <t>TC005 IL MP Find a Pharmacy Link</t>
+  </si>
+  <si>
+    <t>il</t>
+  </si>
+  <si>
+    <t>TC006 NM MP Find a Pharmacy Link</t>
+  </si>
+  <si>
+    <t>nm</t>
+  </si>
+  <si>
+    <t>TC007 WA MP Find a Pharmacy Link</t>
+  </si>
+  <si>
+    <t>wa</t>
+  </si>
+  <si>
+    <t>https://www.caremark.com/pharmacy/benefits/fast/oe/pharmacy-locator/search?fastStyle=OE&amp;oeFillDate=AUTO(01%2F01%2F2023)&amp;BlocksTenant=molina</t>
+  </si>
+  <si>
+    <t>TC008 TX MP Find a Pharmacy Link</t>
+  </si>
+  <si>
+    <t>tx</t>
+  </si>
+  <si>
+    <t>https://www.caremark.com/wps/portal/.cmd/el?id=mo1mp6tx_127&amp;cmxtarget=FRAMED_LOCAL_PHARMACY&amp;newLogin=yes&amp;returnURL=http://www.caremark.com/framedLogoff.html</t>
+  </si>
+  <si>
+    <t>TC009 OH MP Find a Pharmacy Link</t>
+  </si>
+  <si>
+    <t>oh</t>
   </si>
 </sst>
 </file>
@@ -261,10 +361,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -590,19 +686,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="6.8984375" customWidth="1"/>
-    <col min="2" max="2" width="8.8984375" customWidth="1"/>
-    <col min="3" max="3" width="10.8984375" customWidth="1"/>
-    <col min="4" max="4" width="14.8984375" customWidth="1"/>
-    <col min="5" max="5" width="16.8984375" customWidth="1"/>
-    <col min="6" max="6" width="46.8984375" customWidth="1"/>
-    <col min="7" max="7" width="60.8984375" customWidth="1"/>
-    <col min="8" max="8" width="100.8984375" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -628,9 +714,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
@@ -654,9 +740,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
@@ -680,12 +766,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -700,18 +786,18 @@
         <v>11</v>
       </c>
       <c r="G4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
         <v>18</v>
-      </c>
-      <c r="H4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>54</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
@@ -726,18 +812,18 @@
         <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -752,18 +838,18 @@
         <v>11</v>
       </c>
       <c r="G6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>55</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
@@ -778,18 +864,18 @@
         <v>11</v>
       </c>
       <c r="G7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -804,18 +890,18 @@
         <v>11</v>
       </c>
       <c r="G8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
@@ -830,18 +916,18 @@
         <v>11</v>
       </c>
       <c r="G9" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
@@ -856,18 +942,18 @@
         <v>11</v>
       </c>
       <c r="G10" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
@@ -882,18 +968,18 @@
         <v>11</v>
       </c>
       <c r="G11" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
@@ -908,18 +994,18 @@
         <v>11</v>
       </c>
       <c r="G12" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
         <v>14</v>
@@ -934,18 +1020,18 @@
         <v>11</v>
       </c>
       <c r="G13" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -960,18 +1046,18 @@
         <v>11</v>
       </c>
       <c r="G14" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H14" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
         <v>14</v>
@@ -986,18 +1072,18 @@
         <v>11</v>
       </c>
       <c r="G15" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H15" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C16" t="s">
         <v>10</v>
@@ -1012,18 +1098,18 @@
         <v>11</v>
       </c>
       <c r="G16" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="H16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
@@ -1038,18 +1124,18 @@
         <v>11</v>
       </c>
       <c r="G17" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="H17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
@@ -1064,18 +1150,18 @@
         <v>11</v>
       </c>
       <c r="G18" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="H18" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C19" t="s">
         <v>14</v>
@@ -1090,18 +1176,18 @@
         <v>11</v>
       </c>
       <c r="G19" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="H19" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
@@ -1116,18 +1202,18 @@
         <v>11</v>
       </c>
       <c r="G20" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="H20" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C21" t="s">
         <v>14</v>
@@ -1142,22 +1228,352 @@
         <v>11</v>
       </c>
       <c r="G21" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="H21" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H1 A5 C4:H4 C16:H17 C6:H6 C7:H7 C8:H8 C9:H9 C10:H10 C11:H11 C12:H12 C13:H13 C19:H21 C18:H18 C14:H15 C5:H5 B3:H3 B2:H2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:H21" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{5e625f8d-0b53-4f56-9e46-19fa14bb2e5c}" enabled="0" method="" siteId="{5e625f8d-0b53-4f56-9e46-19fa14bb2e5c}" removed="1"/>
-</clbl:labelList>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="31.19921875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I2" t="s">
+        <v>73</v>
+      </c>
+      <c r="J2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I4" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H5" t="s">
+        <v>83</v>
+      </c>
+      <c r="I5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6" t="s">
+        <v>83</v>
+      </c>
+      <c r="I6" t="s">
+        <v>11</v>
+      </c>
+      <c r="J6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H7" t="s">
+        <v>83</v>
+      </c>
+      <c r="I7" t="s">
+        <v>11</v>
+      </c>
+      <c r="J7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H8" t="s">
+        <v>90</v>
+      </c>
+      <c r="I8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" t="s">
+        <v>93</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H9" t="s">
+        <v>93</v>
+      </c>
+      <c r="I9" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H10" t="s">
+        <v>93</v>
+      </c>
+      <c r="I10" t="s">
+        <v>11</v>
+      </c>
+      <c r="J10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:J10" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/data/marketplace/MarketplaceData.xlsx
+++ b/data/marketplace/MarketplaceData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://molinahealthcare-my.sharepoint.com/personal/naresh_jangid_molinahealthcare_com/Documents/Automation/molina_automation/PlanMaterialAutomation/data/marketplace/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_5625D102A8BF400918838D571C15BBF580A02A0F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CB97DC1-37DD-4E2F-9A90-81F054823C70}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_5625D102A8BF400918838D571C15BBF580A02A0F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48662BB8-5DB8-4DE3-9730-2ADE31870552}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -686,9 +686,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -714,7 +714,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -740,7 +740,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -766,7 +766,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -792,7 +792,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -818,7 +818,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -844,7 +844,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -870,7 +870,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -896,7 +896,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -922,7 +922,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -948,7 +948,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -974,7 +974,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -1026,7 +1026,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -1052,7 +1052,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1078,7 +1078,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1104,7 +1104,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -1182,7 +1182,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -1245,12 +1245,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="31.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1282,9 +1282,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
         <v>69</v>
@@ -1314,7 +1314,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1346,9 +1346,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
         <v>78</v>
@@ -1378,9 +1378,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
         <v>81</v>
@@ -1410,9 +1410,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
         <v>84</v>
@@ -1442,9 +1442,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
         <v>86</v>
@@ -1474,9 +1474,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
         <v>88</v>
@@ -1506,9 +1506,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
         <v>91</v>
@@ -1538,9 +1538,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
         <v>94</v>
@@ -1573,7 +1573,13 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:J10" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:J1 A3:J3 B2:J2 B5:J10 B4:J4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{5e625f8d-0b53-4f56-9e46-19fa14bb2e5c}" enabled="0" method="" siteId="{5e625f8d-0b53-4f56-9e46-19fa14bb2e5c}" removed="1"/>
+</clbl:labelList>
 </file>